--- a/project docs/urbanhub_Db.xlsx
+++ b/project docs/urbanhub_Db.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aiubedu60714-my.sharepoint.com/personal/23-50139-1_student_aiub_edu/Documents/uni/10 sem/A .NET/Urbanhub/project docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CAAB226-5146-44EB-A7A4-A8190A84AC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{7CAAB226-5146-44EB-A7A4-A8190A84AC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEB17D2A-9CF0-4C35-9D92-00C7821E012C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{E6CBEEEF-7371-4B4C-B4C6-722456DC993D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{E6CBEEEF-7371-4B4C-B4C6-722456DC993D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="98">
   <si>
     <t>auth</t>
   </si>
@@ -145,9 +145,6 @@
   </si>
   <si>
     <t>log_id(fk)</t>
-  </si>
-  <si>
-    <t>owner</t>
   </si>
   <si>
     <t>history_id(fk)</t>
@@ -922,7 +919,7 @@
     <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" s="11"/>
       <c r="C7" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>1</v>
@@ -931,10 +928,10 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>31</v>
@@ -949,29 +946,29 @@
         <v>20</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="U7" s="1" t="s">
         <v>35</v>
@@ -991,7 +988,7 @@
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>32</v>
@@ -1048,7 +1045,7 @@
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>33</v>
@@ -1105,7 +1102,7 @@
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>33</v>
@@ -1175,7 +1172,7 @@
     <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" s="11"/>
       <c r="C12" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1200,13 +1197,13 @@
     <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" s="11"/>
       <c r="C13" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>35</v>
@@ -1391,11 +1388,11 @@
     </row>
     <row r="26" spans="2:22" ht="21" x14ac:dyDescent="0.35">
       <c r="B26" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
@@ -1443,12 +1440,12 @@
       <c r="D28" s="1"/>
       <c r="E28" s="5"/>
       <c r="F28" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="5"/>
       <c r="I28" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -1468,18 +1465,18 @@
         <v>34</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>17</v>
@@ -1488,19 +1485,19 @@
         <v>31</v>
       </c>
       <c r="L29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M29" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M29" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="N29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O29" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="O29" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P29" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q29" s="1" t="s">
         <v>35</v>
@@ -1532,7 +1529,7 @@
         <v>24</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L30" s="1">
         <v>21212</v>
@@ -1544,7 +1541,7 @@
         <v>50</v>
       </c>
       <c r="O30" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P30" s="1" t="b">
         <v>1</v>
@@ -1579,7 +1576,7 @@
         <v>24</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L31" s="1">
         <v>123123</v>
@@ -1591,7 +1588,7 @@
         <v>70</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P31" s="1" t="b">
         <v>0</v>
@@ -1648,7 +1645,7 @@
     <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" s="11"/>
       <c r="C34" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -1662,7 +1659,7 @@
       <c r="M34" s="1"/>
       <c r="N34" s="5"/>
       <c r="O34" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
@@ -1673,50 +1670,50 @@
     <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35" s="11"/>
       <c r="C35" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>35</v>
       </c>
       <c r="N35" s="5"/>
       <c r="O35" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>35</v>
@@ -1738,7 +1735,7 @@
         <v>40</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>18</v>
@@ -1769,7 +1766,7 @@
         <v>18</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S36" s="1">
         <v>1</v>
@@ -1791,10 +1788,10 @@
         <v>30</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I37" s="1">
         <v>1112</v>
@@ -1822,7 +1819,7 @@
         <v>18</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S37" s="1">
         <v>3</v>
@@ -1844,10 +1841,10 @@
         <v>23</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>19</v>
@@ -1872,10 +1869,10 @@
         <v>43</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S38" s="1">
         <v>2</v>
@@ -1897,10 +1894,10 @@
         <v>49</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>19</v>
@@ -1925,10 +1922,10 @@
         <v>43</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S39" s="1">
         <v>4</v>
@@ -2001,7 +1998,7 @@
     <row r="43" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B43" s="11"/>
       <c r="C43" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -2009,7 +2006,7 @@
       <c r="G43" s="1"/>
       <c r="H43" s="5"/>
       <c r="I43" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -2017,7 +2014,7 @@
       <c r="M43" s="1"/>
       <c r="N43" s="5"/>
       <c r="O43" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
@@ -2028,48 +2025,48 @@
     <row r="44" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B44" s="11"/>
       <c r="C44" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D44" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J44" s="1" t="s">
+      <c r="K44" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="M44" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N44" s="5"/>
       <c r="O44" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P44" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q44" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="R44" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="Q44" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="R44" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="S44" s="5"/>
       <c r="T44" s="12"/>
@@ -2083,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F45" s="1">
         <v>4.5</v>
@@ -2102,7 +2099,7 @@
         <v>2</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M45" s="3">
         <v>46025</v>
@@ -2132,7 +2129,7 @@
         <v>2</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F46" s="1">
         <v>2.5</v>
@@ -2151,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M46" s="3">
         <v>46026</v>
@@ -2181,7 +2178,7 @@
         <v>3</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F47" s="1">
         <v>4</v>
@@ -2200,7 +2197,7 @@
         <v>3</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M47" s="3">
         <v>46027</v>

--- a/project docs/urbanhub_Db.xlsx
+++ b/project docs/urbanhub_Db.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aiubedu60714-my.sharepoint.com/personal/23-50139-1_student_aiub_edu/Documents/uni/10 sem/A .NET/Urbanhub/project docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{7CAAB226-5146-44EB-A7A4-A8190A84AC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEB17D2A-9CF0-4C35-9D92-00C7821E012C}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{7CAAB226-5146-44EB-A7A4-A8190A84AC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADB36F88-5506-45EA-979F-036E0F50C879}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{E6CBEEEF-7371-4B4C-B4C6-722456DC993D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{E6CBEEEF-7371-4B4C-B4C6-722456DC993D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="99">
   <si>
     <t>auth</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>oid(fk)</t>
+  </si>
+  <si>
+    <t>Owner</t>
   </si>
 </sst>
 </file>
@@ -1435,7 +1438,7 @@
     <row r="28" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B28" s="11"/>
       <c r="C28" s="1" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="5"/>
